--- a/etl_test_results.xlsx
+++ b/etl_test_results.xlsx
@@ -2,22 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,8 +24,135 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Cambria"/>
+      <family val="2"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF9C5700"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="35">
     <fill>
       <patternFill/>
     </fill>
@@ -35,12 +161,191 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.7999816888943144"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.5999938962981048"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.3999755851924192"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.7999816888943144"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.5999938962981048"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.3999755851924192"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.7999816888943144"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.5999938962981048"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.3999755851924192"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.7999816888943144"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.5999938962981048"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.3999755851924192"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.7999816888943144"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.5999938962981048"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.3999755851924192"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.7999816888943144"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.5999938962981048"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.3999755851924192"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0090EE90"/>
         <bgColor rgb="0090EE90"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF0000"/>
+        <bgColor rgb="00FF0000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -48,18 +353,208 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.3999755851924192"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="42">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="42">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Title" xfId="1" builtinId="15"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19"/>
+    <cellStyle name="Good" xfId="6" builtinId="26"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28"/>
+    <cellStyle name="Input" xfId="9" builtinId="20"/>
+    <cellStyle name="Output" xfId="10" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11"/>
+    <cellStyle name="Note" xfId="15" builtinId="10"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53"/>
+    <cellStyle name="Total" xfId="17" builtinId="25"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -420,35 +915,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:C361"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Timestamp</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:59:50</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_data_for_sales_file_to_stage</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17 18:58:30</t>
+          <t>2026-09-18 14:59:50</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test_extract_data_for_sales_file_to_stage</t>
+          <t>test_extract_stores_data_from_oracle_to_stag</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
@@ -460,12 +955,12 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17 18:58:30</t>
+          <t>2026-09-18 14:59:50</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>test_extract_stores_data_from_oracle_to_stag</t>
+          <t>test_extract_product_data_from_file_to_stag</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
@@ -477,12 +972,12 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17 18:58:30</t>
+          <t>2026-09-18 14:59:50</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>test_extract_product_data_from_file_to_stag</t>
+          <t>test_extract_inventory_data_from_file_to_stag</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
@@ -494,12 +989,12 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17 18:58:30</t>
+          <t>2026-09-18 14:59:50</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>test_extract_inventory_data_from_file_to_stag</t>
+          <t>test_extract_supplier_data_from_file_to_stag</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -511,12 +1006,12 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17 18:58:30</t>
+          <t>2026-09-18 14:59:50</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>test_extract_supplier_data_from_file_to_stag</t>
+          <t>test_data_loading_for_monthly_sales_summary</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
@@ -528,12 +1023,12 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17 18:58:30</t>
+          <t>2026-09-18 14:59:50</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>test_data_loading_for_monthly_sales_summary</t>
+          <t>test_data_loadin_for_fact_sales</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
@@ -545,12 +1040,12 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17 18:58:30</t>
+          <t>2026-09-18 14:59:50</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>test_data_loadin_for_fact_sales</t>
+          <t>test_data_loading_for_fact_inventory</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
@@ -562,12 +1057,12 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17 18:58:30</t>
+          <t>2026-09-18 14:59:50</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>test_data_loading_for_fact_inventory</t>
+          <t>test_data_loading_for_inventory_levl_by_stores</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
@@ -579,12 +1074,12 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17 18:58:30</t>
+          <t>2026-09-18 14:59:50</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>test_data_loading_for_inventory_levl_by_stores</t>
+          <t>test_duplicates_for_sales_file</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -596,12 +1091,12 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17 18:58:30</t>
+          <t>2026-09-18 14:59:50</t>
         </is>
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>test_duplicates_for_sales_file</t>
+          <t>test_duplicates_for_product_file</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
@@ -613,12 +1108,12 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17 18:58:30</t>
+          <t>2026-09-18 14:59:51</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>test_duplicates_for_product_file</t>
+          <t>test_duplicates_for_inventory_file</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -630,12 +1125,12 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17 18:58:30</t>
+          <t>2026-09-18 14:59:51</t>
         </is>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>test_duplicates_for_inventory_file</t>
+          <t>test_duplicates_for_supplier_file</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
@@ -647,12 +1142,12 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17 18:58:30</t>
+          <t>2026-09-18 14:59:51</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>test_duplicates_for_supplier_file</t>
+          <t>test_null_for_sales_file</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
@@ -664,12 +1159,12 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17 18:58:30</t>
+          <t>2026-09-18 14:59:51</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>test_null_for_sales_file</t>
+          <t>test_null_for_product_file</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
@@ -681,12 +1176,12 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17 18:58:30</t>
+          <t>2026-09-18 14:59:51</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>test_null_for_product_file</t>
+          <t>test_null_for_inventory_file</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
@@ -698,12 +1193,12 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17 18:58:30</t>
+          <t>2026-09-18 14:59:51</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>test_null_for_inventory_file</t>
+          <t>test_null_for_supplier_file</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
@@ -715,12 +1210,12 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17 18:58:31</t>
+          <t>2026-09-18 14:59:51</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>test_null_for_supplier_file</t>
+          <t>test_transform_Filter_Sales</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
@@ -732,12 +1227,12 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17 18:58:31</t>
+          <t>2026-09-18 14:59:51</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>test_transform_Filter_Sales</t>
+          <t>test_transform_Router_High_Sales</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
@@ -749,12 +1244,12 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17 18:58:31</t>
+          <t>2026-09-18 14:59:51</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>test_transform_Router_High_Sales</t>
+          <t>test_transform_Router_Low_Sales</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
@@ -766,12 +1261,12 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17 18:58:31</t>
+          <t>2026-09-18 14:59:51</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>test_transform_Router_Low_Sales</t>
+          <t>test_transform_Aggregator_Sales</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
@@ -783,12 +1278,12 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17 18:58:31</t>
+          <t>2026-09-18 14:59:51</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>test_transform_Aggregator_Sales</t>
+          <t>test_transform_joiner_sales_product_stores</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
@@ -800,12 +1295,12 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17 18:58:31</t>
+          <t>2026-09-18 14:59:51</t>
         </is>
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>test_transform_joiner_sales_product_stores</t>
+          <t>test_transform_Aggregator_Inventory</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
@@ -817,12 +1312,12 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17 18:58:31</t>
+          <t>2026-09-18 14:59:51</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>test_transform_Aggregator_Inventory</t>
+          <t>test_columns_for_monthly_sales_summary</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
@@ -834,12 +1329,12 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17 18:58:31</t>
+          <t>2026-09-18 14:59:51</t>
         </is>
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>test_columns_for_monthly_sales_summary</t>
+          <t>test_columns_for_fact_sales</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
@@ -851,12 +1346,12 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17 18:58:31</t>
+          <t>2026-09-18 14:59:51</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>test_columns_for_fact_sales</t>
+          <t>test_columns_for_fact_inventory</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
@@ -868,12 +1363,12 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17 18:58:31</t>
+          <t>2026-09-18 14:59:52</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>test_columns_for_fact_inventory</t>
+          <t>test_columns_for_inventory_level_by_stores</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
@@ -885,12 +1380,12 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17 18:58:31</t>
+          <t>2026-09-18 14:59:52</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>test_columns_for_inventory_level_by_stores</t>
+          <t>test_dtypes_for_monthly_sales_summary</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
@@ -902,12 +1397,12 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17 18:58:31</t>
+          <t>2026-09-18 14:59:52</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>test_dtypes_for_monthly_sales_summary</t>
+          <t>test_dtypes_for_fact_sales</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
@@ -919,12 +1414,12 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17 18:58:31</t>
+          <t>2026-09-18 14:59:52</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>test_dtypes_for_fact_sales</t>
+          <t>test_dtypes_for_fact_inventory</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
@@ -936,12 +1431,12 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17 18:58:31</t>
+          <t>2026-09-18 14:59:52</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>test_dtypes_for_fact_inventory</t>
+          <t>test_dtypes_for_inventory_level_by_stores</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
@@ -953,15 +1448,5608 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17 18:58:31</t>
+          <t>2026-09-18 15:00:56</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
+          <t>test_extract_data_for_sales_file_to_stage</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00:56</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_stores_data_from_oracle_to_stag</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00:56</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_product_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00:56</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_inventory_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00:56</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_supplier_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00:56</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loading_for_monthly_sales_summary</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00:56</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loadin_for_fact_sales</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00:57</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loading_for_fact_inventory</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00:57</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loading_for_inventory_levl_by_stores</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00:57</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_sales_file</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00:57</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_product_file</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00:57</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_inventory_file</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00:57</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_supplier_file</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00:57</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_sales_file</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00:57</t>
+        </is>
+      </c>
+      <c r="B46" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_product_file</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00:57</t>
+        </is>
+      </c>
+      <c r="B47" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_inventory_file</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00:57</t>
+        </is>
+      </c>
+      <c r="B48" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_supplier_file</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00:57</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Filter_Sales</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00:57</t>
+        </is>
+      </c>
+      <c r="B50" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Router_High_Sales</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00:57</t>
+        </is>
+      </c>
+      <c r="B51" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Router_Low_Sales</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00:58</t>
+        </is>
+      </c>
+      <c r="B52" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Aggregator_Sales</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00:58</t>
+        </is>
+      </c>
+      <c r="B53" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_joiner_sales_product_stores</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00:58</t>
+        </is>
+      </c>
+      <c r="B54" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Aggregator_Inventory</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00:58</t>
+        </is>
+      </c>
+      <c r="B55" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_monthly_sales_summary</t>
+        </is>
+      </c>
+      <c r="C55" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00:58</t>
+        </is>
+      </c>
+      <c r="B56" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_fact_sales</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00:58</t>
+        </is>
+      </c>
+      <c r="B57" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_fact_inventory</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00:58</t>
+        </is>
+      </c>
+      <c r="B58" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_inventory_level_by_stores</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00:58</t>
+        </is>
+      </c>
+      <c r="B59" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_monthly_sales_summary</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00:58</t>
+        </is>
+      </c>
+      <c r="B60" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_fact_sales</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00:58</t>
+        </is>
+      </c>
+      <c r="B61" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_fact_inventory</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00:58</t>
+        </is>
+      </c>
+      <c r="B62" s="1" t="inlineStr">
+        <is>
           <t>test_dtypes_for_inventory_level_by_stores</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:01:19</t>
+        </is>
+      </c>
+      <c r="B63" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_data_for_sales_file_to_stage</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:01:19</t>
+        </is>
+      </c>
+      <c r="B64" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_stores_data_from_oracle_to_stag</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:01:20</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loadin_for_fact_sales</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:01:20</t>
+        </is>
+      </c>
+      <c r="B66" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loading_for_fact_inventory</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:01:20</t>
+        </is>
+      </c>
+      <c r="B67" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loading_for_inventory_levl_by_stores</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:00</t>
+        </is>
+      </c>
+      <c r="B68" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_data_for_sales_file_to_stage</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:00</t>
+        </is>
+      </c>
+      <c r="B69" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_stores_data_from_oracle_to_stag</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:01</t>
+        </is>
+      </c>
+      <c r="B70" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_product_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:01</t>
+        </is>
+      </c>
+      <c r="B71" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_inventory_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:01</t>
+        </is>
+      </c>
+      <c r="B72" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_supplier_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:01</t>
+        </is>
+      </c>
+      <c r="B73" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loading_for_monthly_sales_summary</t>
+        </is>
+      </c>
+      <c r="C73" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:01</t>
+        </is>
+      </c>
+      <c r="B74" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loadin_for_fact_sales</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:01</t>
+        </is>
+      </c>
+      <c r="B75" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loading_for_fact_inventory</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:01</t>
+        </is>
+      </c>
+      <c r="B76" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loading_for_inventory_levl_by_stores</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:01</t>
+        </is>
+      </c>
+      <c r="B77" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_sales_file</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:01</t>
+        </is>
+      </c>
+      <c r="B78" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_product_file</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:01</t>
+        </is>
+      </c>
+      <c r="B79" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_inventory_file</t>
+        </is>
+      </c>
+      <c r="C79" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:01</t>
+        </is>
+      </c>
+      <c r="B80" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_supplier_file</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:01</t>
+        </is>
+      </c>
+      <c r="B81" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_sales_file</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:02</t>
+        </is>
+      </c>
+      <c r="B82" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_product_file</t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:02</t>
+        </is>
+      </c>
+      <c r="B83" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_inventory_file</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:02</t>
+        </is>
+      </c>
+      <c r="B84" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_supplier_file</t>
+        </is>
+      </c>
+      <c r="C84" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:02</t>
+        </is>
+      </c>
+      <c r="B85" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Filter_Sales</t>
+        </is>
+      </c>
+      <c r="C85" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:02</t>
+        </is>
+      </c>
+      <c r="B86" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Router_High_Sales</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:02</t>
+        </is>
+      </c>
+      <c r="B87" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Router_Low_Sales</t>
+        </is>
+      </c>
+      <c r="C87" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:02</t>
+        </is>
+      </c>
+      <c r="B88" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Aggregator_Sales</t>
+        </is>
+      </c>
+      <c r="C88" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:02</t>
+        </is>
+      </c>
+      <c r="B89" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_joiner_sales_product_stores</t>
+        </is>
+      </c>
+      <c r="C89" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:02</t>
+        </is>
+      </c>
+      <c r="B90" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Aggregator_Inventory</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:02</t>
+        </is>
+      </c>
+      <c r="B91" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_monthly_sales_summary</t>
+        </is>
+      </c>
+      <c r="C91" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:02</t>
+        </is>
+      </c>
+      <c r="B92" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_fact_sales</t>
+        </is>
+      </c>
+      <c r="C92" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:02</t>
+        </is>
+      </c>
+      <c r="B93" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_fact_inventory</t>
+        </is>
+      </c>
+      <c r="C93" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:02</t>
+        </is>
+      </c>
+      <c r="B94" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_inventory_level_by_stores</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:03</t>
+        </is>
+      </c>
+      <c r="B95" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_monthly_sales_summary</t>
+        </is>
+      </c>
+      <c r="C95" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:03</t>
+        </is>
+      </c>
+      <c r="B96" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_fact_sales</t>
+        </is>
+      </c>
+      <c r="C96" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:03</t>
+        </is>
+      </c>
+      <c r="B97" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_fact_inventory</t>
+        </is>
+      </c>
+      <c r="C97" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:03</t>
+        </is>
+      </c>
+      <c r="B98" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_inventory_level_by_stores</t>
+        </is>
+      </c>
+      <c r="C98" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:23</t>
+        </is>
+      </c>
+      <c r="B99" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_data_for_sales_file_to_stage</t>
+        </is>
+      </c>
+      <c r="C99" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:23</t>
+        </is>
+      </c>
+      <c r="B100" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_stores_data_from_oracle_to_stag</t>
+        </is>
+      </c>
+      <c r="C100" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:23</t>
+        </is>
+      </c>
+      <c r="B101" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_product_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C101" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:23</t>
+        </is>
+      </c>
+      <c r="B102" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_inventory_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C102" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:23</t>
+        </is>
+      </c>
+      <c r="B103" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loading_for_inventory_levl_by_stores</t>
+        </is>
+      </c>
+      <c r="C103" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:23</t>
+        </is>
+      </c>
+      <c r="B104" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_sales_file</t>
+        </is>
+      </c>
+      <c r="C104" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:23</t>
+        </is>
+      </c>
+      <c r="B105" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_product_file</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:23</t>
+        </is>
+      </c>
+      <c r="B106" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_inventory_file</t>
+        </is>
+      </c>
+      <c r="C106" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:23</t>
+        </is>
+      </c>
+      <c r="B107" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_supplier_file</t>
+        </is>
+      </c>
+      <c r="C107" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:23</t>
+        </is>
+      </c>
+      <c r="B108" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_sales_file</t>
+        </is>
+      </c>
+      <c r="C108" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:23</t>
+        </is>
+      </c>
+      <c r="B109" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_product_file</t>
+        </is>
+      </c>
+      <c r="C109" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:24</t>
+        </is>
+      </c>
+      <c r="B110" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_inventory_file</t>
+        </is>
+      </c>
+      <c r="C110" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:41</t>
+        </is>
+      </c>
+      <c r="B111" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_data_for_sales_file_to_stage</t>
+        </is>
+      </c>
+      <c r="C111" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:41</t>
+        </is>
+      </c>
+      <c r="B112" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_stores_data_from_oracle_to_stag</t>
+        </is>
+      </c>
+      <c r="C112" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:41</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_product_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C113" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:42</t>
+        </is>
+      </c>
+      <c r="B114" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_inventory_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C114" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:42</t>
+        </is>
+      </c>
+      <c r="B115" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_supplier_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C115" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:42</t>
+        </is>
+      </c>
+      <c r="B116" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loading_for_monthly_sales_summary</t>
+        </is>
+      </c>
+      <c r="C116" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:42</t>
+        </is>
+      </c>
+      <c r="B117" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loadin_for_fact_sales</t>
+        </is>
+      </c>
+      <c r="C117" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:42</t>
+        </is>
+      </c>
+      <c r="B118" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loading_for_fact_inventory</t>
+        </is>
+      </c>
+      <c r="C118" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:42</t>
+        </is>
+      </c>
+      <c r="B119" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loading_for_inventory_levl_by_stores</t>
+        </is>
+      </c>
+      <c r="C119" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:42</t>
+        </is>
+      </c>
+      <c r="B120" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_sales_file</t>
+        </is>
+      </c>
+      <c r="C120" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:42</t>
+        </is>
+      </c>
+      <c r="B121" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_product_file</t>
+        </is>
+      </c>
+      <c r="C121" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:42</t>
+        </is>
+      </c>
+      <c r="B122" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_inventory_file</t>
+        </is>
+      </c>
+      <c r="C122" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:42</t>
+        </is>
+      </c>
+      <c r="B123" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_supplier_file</t>
+        </is>
+      </c>
+      <c r="C123" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:42</t>
+        </is>
+      </c>
+      <c r="B124" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_sales_file</t>
+        </is>
+      </c>
+      <c r="C124" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:42</t>
+        </is>
+      </c>
+      <c r="B125" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_product_file</t>
+        </is>
+      </c>
+      <c r="C125" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:43</t>
+        </is>
+      </c>
+      <c r="B126" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_inventory_file</t>
+        </is>
+      </c>
+      <c r="C126" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:43</t>
+        </is>
+      </c>
+      <c r="B127" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_supplier_file</t>
+        </is>
+      </c>
+      <c r="C127" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:43</t>
+        </is>
+      </c>
+      <c r="B128" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Filter_Sales</t>
+        </is>
+      </c>
+      <c r="C128" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:43</t>
+        </is>
+      </c>
+      <c r="B129" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Router_High_Sales</t>
+        </is>
+      </c>
+      <c r="C129" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:43</t>
+        </is>
+      </c>
+      <c r="B130" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Router_Low_Sales</t>
+        </is>
+      </c>
+      <c r="C130" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:43</t>
+        </is>
+      </c>
+      <c r="B131" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Aggregator_Sales</t>
+        </is>
+      </c>
+      <c r="C131" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:43</t>
+        </is>
+      </c>
+      <c r="B132" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_joiner_sales_product_stores</t>
+        </is>
+      </c>
+      <c r="C132" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:43</t>
+        </is>
+      </c>
+      <c r="B133" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Aggregator_Inventory</t>
+        </is>
+      </c>
+      <c r="C133" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:43</t>
+        </is>
+      </c>
+      <c r="B134" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_monthly_sales_summary</t>
+        </is>
+      </c>
+      <c r="C134" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:43</t>
+        </is>
+      </c>
+      <c r="B135" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_fact_sales</t>
+        </is>
+      </c>
+      <c r="C135" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:43</t>
+        </is>
+      </c>
+      <c r="B136" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_fact_inventory</t>
+        </is>
+      </c>
+      <c r="C136" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:43</t>
+        </is>
+      </c>
+      <c r="B137" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_inventory_level_by_stores</t>
+        </is>
+      </c>
+      <c r="C137" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:43</t>
+        </is>
+      </c>
+      <c r="B138" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_monthly_sales_summary</t>
+        </is>
+      </c>
+      <c r="C138" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:44</t>
+        </is>
+      </c>
+      <c r="B139" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_fact_sales</t>
+        </is>
+      </c>
+      <c r="C139" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:44</t>
+        </is>
+      </c>
+      <c r="B140" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_fact_inventory</t>
+        </is>
+      </c>
+      <c r="C140" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:02:44</t>
+        </is>
+      </c>
+      <c r="B141" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_inventory_level_by_stores</t>
+        </is>
+      </c>
+      <c r="C141" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:35</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>test_extract_data_for_sales_file_to_stage</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:40</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>test_extract_data_for_sales_file_to_stage</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:45</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>test_extract_data_for_sales_file_to_stage</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:45</t>
+        </is>
+      </c>
+      <c r="B145" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_stores_data_from_oracle_to_stag</t>
+        </is>
+      </c>
+      <c r="C145" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:45</t>
+        </is>
+      </c>
+      <c r="B146" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_product_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C146" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:45</t>
+        </is>
+      </c>
+      <c r="B147" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_inventory_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C147" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:45</t>
+        </is>
+      </c>
+      <c r="B148" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_supplier_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C148" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:45</t>
+        </is>
+      </c>
+      <c r="B149" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loading_for_monthly_sales_summary</t>
+        </is>
+      </c>
+      <c r="C149" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:45</t>
+        </is>
+      </c>
+      <c r="B150" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loadin_for_fact_sales</t>
+        </is>
+      </c>
+      <c r="C150" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:45</t>
+        </is>
+      </c>
+      <c r="B151" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loading_for_fact_inventory</t>
+        </is>
+      </c>
+      <c r="C151" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:45</t>
+        </is>
+      </c>
+      <c r="B152" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loading_for_inventory_levl_by_stores</t>
+        </is>
+      </c>
+      <c r="C152" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:46</t>
+        </is>
+      </c>
+      <c r="B153" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_sales_file</t>
+        </is>
+      </c>
+      <c r="C153" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:46</t>
+        </is>
+      </c>
+      <c r="B154" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_product_file</t>
+        </is>
+      </c>
+      <c r="C154" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:46</t>
+        </is>
+      </c>
+      <c r="B155" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_inventory_file</t>
+        </is>
+      </c>
+      <c r="C155" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:46</t>
+        </is>
+      </c>
+      <c r="B156" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_supplier_file</t>
+        </is>
+      </c>
+      <c r="C156" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:46</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>test_null_for_sales_file</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:51</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>test_null_for_sales_file</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:56</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>test_null_for_sales_file</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:56</t>
+        </is>
+      </c>
+      <c r="B160" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_product_file</t>
+        </is>
+      </c>
+      <c r="C160" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:56</t>
+        </is>
+      </c>
+      <c r="B161" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_inventory_file</t>
+        </is>
+      </c>
+      <c r="C161" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:56</t>
+        </is>
+      </c>
+      <c r="B162" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_supplier_file</t>
+        </is>
+      </c>
+      <c r="C162" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:56</t>
+        </is>
+      </c>
+      <c r="B163" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Filter_Sales</t>
+        </is>
+      </c>
+      <c r="C163" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:57</t>
+        </is>
+      </c>
+      <c r="B164" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Router_High_Sales</t>
+        </is>
+      </c>
+      <c r="C164" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:57</t>
+        </is>
+      </c>
+      <c r="B165" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Router_Low_Sales</t>
+        </is>
+      </c>
+      <c r="C165" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:57</t>
+        </is>
+      </c>
+      <c r="B166" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Aggregator_Sales</t>
+        </is>
+      </c>
+      <c r="C166" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:57</t>
+        </is>
+      </c>
+      <c r="B167" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_joiner_sales_product_stores</t>
+        </is>
+      </c>
+      <c r="C167" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:57</t>
+        </is>
+      </c>
+      <c r="B168" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Aggregator_Inventory</t>
+        </is>
+      </c>
+      <c r="C168" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:57</t>
+        </is>
+      </c>
+      <c r="B169" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_monthly_sales_summary</t>
+        </is>
+      </c>
+      <c r="C169" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:57</t>
+        </is>
+      </c>
+      <c r="B170" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_fact_sales</t>
+        </is>
+      </c>
+      <c r="C170" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:57</t>
+        </is>
+      </c>
+      <c r="B171" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_fact_inventory</t>
+        </is>
+      </c>
+      <c r="C171" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:57</t>
+        </is>
+      </c>
+      <c r="B172" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_inventory_level_by_stores</t>
+        </is>
+      </c>
+      <c r="C172" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:57</t>
+        </is>
+      </c>
+      <c r="B173" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_monthly_sales_summary</t>
+        </is>
+      </c>
+      <c r="C173" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:57</t>
+        </is>
+      </c>
+      <c r="B174" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_fact_sales</t>
+        </is>
+      </c>
+      <c r="C174" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:58</t>
+        </is>
+      </c>
+      <c r="B175" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_fact_inventory</t>
+        </is>
+      </c>
+      <c r="C175" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:03:58</t>
+        </is>
+      </c>
+      <c r="B176" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_inventory_level_by_stores</t>
+        </is>
+      </c>
+      <c r="C176" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:22</t>
+        </is>
+      </c>
+      <c r="B177" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_data_for_sales_file_to_stage</t>
+        </is>
+      </c>
+      <c r="C177" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:23</t>
+        </is>
+      </c>
+      <c r="B178" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_stores_data_from_oracle_to_stag</t>
+        </is>
+      </c>
+      <c r="C178" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:23</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>test_extract_product_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:28</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>test_extract_product_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:33</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>test_extract_product_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:34</t>
+        </is>
+      </c>
+      <c r="B182" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_inventory_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C182" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:34</t>
+        </is>
+      </c>
+      <c r="B183" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_supplier_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C183" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:34</t>
+        </is>
+      </c>
+      <c r="B184" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loading_for_monthly_sales_summary</t>
+        </is>
+      </c>
+      <c r="C184" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:34</t>
+        </is>
+      </c>
+      <c r="B185" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loadin_for_fact_sales</t>
+        </is>
+      </c>
+      <c r="C185" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:34</t>
+        </is>
+      </c>
+      <c r="B186" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loading_for_fact_inventory</t>
+        </is>
+      </c>
+      <c r="C186" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:34</t>
+        </is>
+      </c>
+      <c r="B187" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loading_for_inventory_levl_by_stores</t>
+        </is>
+      </c>
+      <c r="C187" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:34</t>
+        </is>
+      </c>
+      <c r="B188" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_sales_file</t>
+        </is>
+      </c>
+      <c r="C188" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:34</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_product_file</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:40</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_product_file</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:45</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_product_file</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:45</t>
+        </is>
+      </c>
+      <c r="B192" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_inventory_file</t>
+        </is>
+      </c>
+      <c r="C192" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:45</t>
+        </is>
+      </c>
+      <c r="B193" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_supplier_file</t>
+        </is>
+      </c>
+      <c r="C193" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:45</t>
+        </is>
+      </c>
+      <c r="B194" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_sales_file</t>
+        </is>
+      </c>
+      <c r="C194" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:45</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>test_null_for_product_file</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:50</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>test_null_for_product_file</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:55</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>test_null_for_product_file</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:56</t>
+        </is>
+      </c>
+      <c r="B198" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_inventory_file</t>
+        </is>
+      </c>
+      <c r="C198" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:56</t>
+        </is>
+      </c>
+      <c r="B199" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_supplier_file</t>
+        </is>
+      </c>
+      <c r="C199" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:56</t>
+        </is>
+      </c>
+      <c r="B200" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Filter_Sales</t>
+        </is>
+      </c>
+      <c r="C200" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:56</t>
+        </is>
+      </c>
+      <c r="B201" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Router_High_Sales</t>
+        </is>
+      </c>
+      <c r="C201" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:56</t>
+        </is>
+      </c>
+      <c r="B202" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Router_Low_Sales</t>
+        </is>
+      </c>
+      <c r="C202" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:56</t>
+        </is>
+      </c>
+      <c r="B203" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Aggregator_Sales</t>
+        </is>
+      </c>
+      <c r="C203" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:56</t>
+        </is>
+      </c>
+      <c r="B204" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_joiner_sales_product_stores</t>
+        </is>
+      </c>
+      <c r="C204" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:56</t>
+        </is>
+      </c>
+      <c r="B205" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Aggregator_Inventory</t>
+        </is>
+      </c>
+      <c r="C205" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:56</t>
+        </is>
+      </c>
+      <c r="B206" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_monthly_sales_summary</t>
+        </is>
+      </c>
+      <c r="C206" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:56</t>
+        </is>
+      </c>
+      <c r="B207" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_fact_sales</t>
+        </is>
+      </c>
+      <c r="C207" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:56</t>
+        </is>
+      </c>
+      <c r="B208" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_fact_inventory</t>
+        </is>
+      </c>
+      <c r="C208" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:57</t>
+        </is>
+      </c>
+      <c r="B209" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_inventory_level_by_stores</t>
+        </is>
+      </c>
+      <c r="C209" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:57</t>
+        </is>
+      </c>
+      <c r="B210" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_monthly_sales_summary</t>
+        </is>
+      </c>
+      <c r="C210" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:57</t>
+        </is>
+      </c>
+      <c r="B211" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_fact_sales</t>
+        </is>
+      </c>
+      <c r="C211" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:57</t>
+        </is>
+      </c>
+      <c r="B212" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_fact_inventory</t>
+        </is>
+      </c>
+      <c r="C212" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:20:57</t>
+        </is>
+      </c>
+      <c r="B213" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_inventory_level_by_stores</t>
+        </is>
+      </c>
+      <c r="C213" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:24:48</t>
+        </is>
+      </c>
+      <c r="B214" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_data_for_sales_file_to_stage</t>
+        </is>
+      </c>
+      <c r="C214" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:24:48</t>
+        </is>
+      </c>
+      <c r="B215" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_stores_data_from_oracle_to_stag</t>
+        </is>
+      </c>
+      <c r="C215" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:24:48</t>
+        </is>
+      </c>
+      <c r="B216" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_product_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C216" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:24:48</t>
+        </is>
+      </c>
+      <c r="B217" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_inventory_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C217" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:24:48</t>
+        </is>
+      </c>
+      <c r="B218" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_supplier_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C218" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:24:48</t>
+        </is>
+      </c>
+      <c r="B219" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loading_for_monthly_sales_summary</t>
+        </is>
+      </c>
+      <c r="C219" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:24:48</t>
+        </is>
+      </c>
+      <c r="B220" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loadin_for_fact_sales</t>
+        </is>
+      </c>
+      <c r="C220" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:24:48</t>
+        </is>
+      </c>
+      <c r="B221" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loading_for_fact_inventory</t>
+        </is>
+      </c>
+      <c r="C221" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:24:48</t>
+        </is>
+      </c>
+      <c r="B222" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loading_for_inventory_levl_by_stores</t>
+        </is>
+      </c>
+      <c r="C222" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:24:48</t>
+        </is>
+      </c>
+      <c r="B223" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_sales_file</t>
+        </is>
+      </c>
+      <c r="C223" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:24:49</t>
+        </is>
+      </c>
+      <c r="B224" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_product_file</t>
+        </is>
+      </c>
+      <c r="C224" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:24:49</t>
+        </is>
+      </c>
+      <c r="B225" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_inventory_file</t>
+        </is>
+      </c>
+      <c r="C225" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:24:49</t>
+        </is>
+      </c>
+      <c r="B226" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_supplier_file</t>
+        </is>
+      </c>
+      <c r="C226" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:24:49</t>
+        </is>
+      </c>
+      <c r="B227" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_sales_file</t>
+        </is>
+      </c>
+      <c r="C227" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:24:49</t>
+        </is>
+      </c>
+      <c r="B228" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_product_file</t>
+        </is>
+      </c>
+      <c r="C228" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:24:49</t>
+        </is>
+      </c>
+      <c r="B229" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_inventory_file</t>
+        </is>
+      </c>
+      <c r="C229" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:24:49</t>
+        </is>
+      </c>
+      <c r="B230" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_supplier_file</t>
+        </is>
+      </c>
+      <c r="C230" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:24:49</t>
+        </is>
+      </c>
+      <c r="B231" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Filter_Sales</t>
+        </is>
+      </c>
+      <c r="C231" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:24:49</t>
+        </is>
+      </c>
+      <c r="B232" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Router_High_Sales</t>
+        </is>
+      </c>
+      <c r="C232" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:24:49</t>
+        </is>
+      </c>
+      <c r="B233" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Router_Low_Sales</t>
+        </is>
+      </c>
+      <c r="C233" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:24:49</t>
+        </is>
+      </c>
+      <c r="B234" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Aggregator_Sales</t>
+        </is>
+      </c>
+      <c r="C234" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:24:50</t>
+        </is>
+      </c>
+      <c r="B235" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_joiner_sales_product_stores</t>
+        </is>
+      </c>
+      <c r="C235" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:24:50</t>
+        </is>
+      </c>
+      <c r="B236" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Aggregator_Inventory</t>
+        </is>
+      </c>
+      <c r="C236" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:24:50</t>
+        </is>
+      </c>
+      <c r="B237" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_monthly_sales_summary</t>
+        </is>
+      </c>
+      <c r="C237" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:24:50</t>
+        </is>
+      </c>
+      <c r="B238" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_fact_sales</t>
+        </is>
+      </c>
+      <c r="C238" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:24:50</t>
+        </is>
+      </c>
+      <c r="B239" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_fact_inventory</t>
+        </is>
+      </c>
+      <c r="C239" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:24:50</t>
+        </is>
+      </c>
+      <c r="B240" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_inventory_level_by_stores</t>
+        </is>
+      </c>
+      <c r="C240" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:24:50</t>
+        </is>
+      </c>
+      <c r="B241" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_monthly_sales_summary</t>
+        </is>
+      </c>
+      <c r="C241" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:24:50</t>
+        </is>
+      </c>
+      <c r="B242" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_fact_sales</t>
+        </is>
+      </c>
+      <c r="C242" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:24:50</t>
+        </is>
+      </c>
+      <c r="B243" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_fact_inventory</t>
+        </is>
+      </c>
+      <c r="C243" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:24:50</t>
+        </is>
+      </c>
+      <c r="B244" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_inventory_level_by_stores</t>
+        </is>
+      </c>
+      <c r="C244" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:32:34</t>
+        </is>
+      </c>
+      <c r="B245" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_sales_file</t>
+        </is>
+      </c>
+      <c r="C245" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:32:34</t>
+        </is>
+      </c>
+      <c r="B246" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_product_file</t>
+        </is>
+      </c>
+      <c r="C246" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:32:34</t>
+        </is>
+      </c>
+      <c r="B247" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_inventory_file</t>
+        </is>
+      </c>
+      <c r="C247" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:32:34</t>
+        </is>
+      </c>
+      <c r="B248" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_supplier_file</t>
+        </is>
+      </c>
+      <c r="C248" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:32:35</t>
+        </is>
+      </c>
+      <c r="B249" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_sales_file</t>
+        </is>
+      </c>
+      <c r="C249" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:32:35</t>
+        </is>
+      </c>
+      <c r="B250" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_product_file</t>
+        </is>
+      </c>
+      <c r="C250" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:32:35</t>
+        </is>
+      </c>
+      <c r="B251" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_inventory_file</t>
+        </is>
+      </c>
+      <c r="C251" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:32:35</t>
+        </is>
+      </c>
+      <c r="B252" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_supplier_file</t>
+        </is>
+      </c>
+      <c r="C252" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:33:37</t>
+        </is>
+      </c>
+      <c r="B253" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_sales_file</t>
+        </is>
+      </c>
+      <c r="C253" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:33:37</t>
+        </is>
+      </c>
+      <c r="B254" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_product_file</t>
+        </is>
+      </c>
+      <c r="C254" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:33:37</t>
+        </is>
+      </c>
+      <c r="B255" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_inventory_file</t>
+        </is>
+      </c>
+      <c r="C255" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:33:37</t>
+        </is>
+      </c>
+      <c r="B256" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_supplier_file</t>
+        </is>
+      </c>
+      <c r="C256" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:33:37</t>
+        </is>
+      </c>
+      <c r="B257" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_sales_file</t>
+        </is>
+      </c>
+      <c r="C257" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:33:37</t>
+        </is>
+      </c>
+      <c r="B258" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_product_file</t>
+        </is>
+      </c>
+      <c r="C258" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:33:38</t>
+        </is>
+      </c>
+      <c r="B259" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_inventory_file</t>
+        </is>
+      </c>
+      <c r="C259" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:33:38</t>
+        </is>
+      </c>
+      <c r="B260" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_supplier_file</t>
+        </is>
+      </c>
+      <c r="C260" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:36:34</t>
+        </is>
+      </c>
+      <c r="B261" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_data_for_sales_file_to_stage</t>
+        </is>
+      </c>
+      <c r="C261" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:36:34</t>
+        </is>
+      </c>
+      <c r="B262" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_stores_data_from_oracle_to_stag</t>
+        </is>
+      </c>
+      <c r="C262" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:36:34</t>
+        </is>
+      </c>
+      <c r="B263" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_product_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C263" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:36:34</t>
+        </is>
+      </c>
+      <c r="B264" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_inventory_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C264" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:36:34</t>
+        </is>
+      </c>
+      <c r="B265" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_supplier_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C265" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:36:34</t>
+        </is>
+      </c>
+      <c r="B266" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loading_for_monthly_sales_summary</t>
+        </is>
+      </c>
+      <c r="C266" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:36:35</t>
+        </is>
+      </c>
+      <c r="B267" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loadin_for_fact_sales</t>
+        </is>
+      </c>
+      <c r="C267" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:36:35</t>
+        </is>
+      </c>
+      <c r="B268" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loading_for_fact_inventory</t>
+        </is>
+      </c>
+      <c r="C268" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:36:35</t>
+        </is>
+      </c>
+      <c r="B269" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loading_for_inventory_levl_by_stores</t>
+        </is>
+      </c>
+      <c r="C269" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:36:35</t>
+        </is>
+      </c>
+      <c r="B270" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_sales_file</t>
+        </is>
+      </c>
+      <c r="C270" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:36:35</t>
+        </is>
+      </c>
+      <c r="B271" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_product_file</t>
+        </is>
+      </c>
+      <c r="C271" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:36:35</t>
+        </is>
+      </c>
+      <c r="B272" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_inventory_file</t>
+        </is>
+      </c>
+      <c r="C272" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:36:35</t>
+        </is>
+      </c>
+      <c r="B273" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_supplier_file</t>
+        </is>
+      </c>
+      <c r="C273" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:36:35</t>
+        </is>
+      </c>
+      <c r="B274" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_sales_file</t>
+        </is>
+      </c>
+      <c r="C274" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:36:35</t>
+        </is>
+      </c>
+      <c r="B275" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_product_file</t>
+        </is>
+      </c>
+      <c r="C275" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:36:35</t>
+        </is>
+      </c>
+      <c r="B276" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_inventory_file</t>
+        </is>
+      </c>
+      <c r="C276" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:36:36</t>
+        </is>
+      </c>
+      <c r="B277" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_supplier_file</t>
+        </is>
+      </c>
+      <c r="C277" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:36:36</t>
+        </is>
+      </c>
+      <c r="B278" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Filter_Sales</t>
+        </is>
+      </c>
+      <c r="C278" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:36:36</t>
+        </is>
+      </c>
+      <c r="B279" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Router_High_Sales</t>
+        </is>
+      </c>
+      <c r="C279" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:36:36</t>
+        </is>
+      </c>
+      <c r="B280" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Router_Low_Sales</t>
+        </is>
+      </c>
+      <c r="C280" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:36:36</t>
+        </is>
+      </c>
+      <c r="B281" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Aggregator_Sales</t>
+        </is>
+      </c>
+      <c r="C281" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:36:36</t>
+        </is>
+      </c>
+      <c r="B282" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_joiner_sales_product_stores</t>
+        </is>
+      </c>
+      <c r="C282" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:36:36</t>
+        </is>
+      </c>
+      <c r="B283" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Aggregator_Inventory</t>
+        </is>
+      </c>
+      <c r="C283" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:36:36</t>
+        </is>
+      </c>
+      <c r="B284" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_monthly_sales_summary</t>
+        </is>
+      </c>
+      <c r="C284" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:36:36</t>
+        </is>
+      </c>
+      <c r="B285" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_fact_sales</t>
+        </is>
+      </c>
+      <c r="C285" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:36:36</t>
+        </is>
+      </c>
+      <c r="B286" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_fact_inventory</t>
+        </is>
+      </c>
+      <c r="C286" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:36:36</t>
+        </is>
+      </c>
+      <c r="B287" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_inventory_level_by_stores</t>
+        </is>
+      </c>
+      <c r="C287" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:36:37</t>
+        </is>
+      </c>
+      <c r="B288" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_monthly_sales_summary</t>
+        </is>
+      </c>
+      <c r="C288" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:36:37</t>
+        </is>
+      </c>
+      <c r="B289" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_fact_sales</t>
+        </is>
+      </c>
+      <c r="C289" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:36:37</t>
+        </is>
+      </c>
+      <c r="B290" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_fact_inventory</t>
+        </is>
+      </c>
+      <c r="C290" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:36:37</t>
+        </is>
+      </c>
+      <c r="B291" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_inventory_level_by_stores</t>
+        </is>
+      </c>
+      <c r="C291" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:40:40</t>
+        </is>
+      </c>
+      <c r="B292" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_sales_file</t>
+        </is>
+      </c>
+      <c r="C292" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:40:40</t>
+        </is>
+      </c>
+      <c r="B293" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_product_file</t>
+        </is>
+      </c>
+      <c r="C293" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:40:40</t>
+        </is>
+      </c>
+      <c r="B294" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_inventory_file</t>
+        </is>
+      </c>
+      <c r="C294" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:40:40</t>
+        </is>
+      </c>
+      <c r="B295" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_supplier_file</t>
+        </is>
+      </c>
+      <c r="C295" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:40:40</t>
+        </is>
+      </c>
+      <c r="B296" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_sales_file</t>
+        </is>
+      </c>
+      <c r="C296" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:40:40</t>
+        </is>
+      </c>
+      <c r="B297" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_product_file</t>
+        </is>
+      </c>
+      <c r="C297" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:40:40</t>
+        </is>
+      </c>
+      <c r="B298" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_inventory_file</t>
+        </is>
+      </c>
+      <c r="C298" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:40:40</t>
+        </is>
+      </c>
+      <c r="B299" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_supplier_file</t>
+        </is>
+      </c>
+      <c r="C299" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:42:52</t>
+        </is>
+      </c>
+      <c r="B300" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_data_for_sales_file_to_stage</t>
+        </is>
+      </c>
+      <c r="C300" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:42:52</t>
+        </is>
+      </c>
+      <c r="B301" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_stores_data_from_oracle_to_stag</t>
+        </is>
+      </c>
+      <c r="C301" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:42:52</t>
+        </is>
+      </c>
+      <c r="B302" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_product_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C302" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:42:53</t>
+        </is>
+      </c>
+      <c r="B303" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_inventory_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C303" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:42:53</t>
+        </is>
+      </c>
+      <c r="B304" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_supplier_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C304" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:42:53</t>
+        </is>
+      </c>
+      <c r="B305" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loading_for_monthly_sales_summary</t>
+        </is>
+      </c>
+      <c r="C305" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:42:53</t>
+        </is>
+      </c>
+      <c r="B306" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loadin_for_fact_sales</t>
+        </is>
+      </c>
+      <c r="C306" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:42:53</t>
+        </is>
+      </c>
+      <c r="B307" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loading_for_fact_inventory</t>
+        </is>
+      </c>
+      <c r="C307" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:42:53</t>
+        </is>
+      </c>
+      <c r="B308" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loading_for_inventory_levl_by_stores</t>
+        </is>
+      </c>
+      <c r="C308" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:42:53</t>
+        </is>
+      </c>
+      <c r="B309" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_sales_file</t>
+        </is>
+      </c>
+      <c r="C309" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:42:53</t>
+        </is>
+      </c>
+      <c r="B310" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_product_file</t>
+        </is>
+      </c>
+      <c r="C310" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:42:53</t>
+        </is>
+      </c>
+      <c r="B311" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_inventory_file</t>
+        </is>
+      </c>
+      <c r="C311" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:42:53</t>
+        </is>
+      </c>
+      <c r="B312" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_supplier_file</t>
+        </is>
+      </c>
+      <c r="C312" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:42:54</t>
+        </is>
+      </c>
+      <c r="B313" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_sales_file</t>
+        </is>
+      </c>
+      <c r="C313" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:42:54</t>
+        </is>
+      </c>
+      <c r="B314" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_product_file</t>
+        </is>
+      </c>
+      <c r="C314" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:42:54</t>
+        </is>
+      </c>
+      <c r="B315" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_inventory_file</t>
+        </is>
+      </c>
+      <c r="C315" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:42:54</t>
+        </is>
+      </c>
+      <c r="B316" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_supplier_file</t>
+        </is>
+      </c>
+      <c r="C316" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:42:54</t>
+        </is>
+      </c>
+      <c r="B317" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Filter_Sales</t>
+        </is>
+      </c>
+      <c r="C317" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:42:54</t>
+        </is>
+      </c>
+      <c r="B318" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Router_High_Sales</t>
+        </is>
+      </c>
+      <c r="C318" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:42:54</t>
+        </is>
+      </c>
+      <c r="B319" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Router_Low_Sales</t>
+        </is>
+      </c>
+      <c r="C319" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:42:54</t>
+        </is>
+      </c>
+      <c r="B320" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Aggregator_Sales</t>
+        </is>
+      </c>
+      <c r="C320" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:42:55</t>
+        </is>
+      </c>
+      <c r="B321" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_joiner_sales_product_stores</t>
+        </is>
+      </c>
+      <c r="C321" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:42:55</t>
+        </is>
+      </c>
+      <c r="B322" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Aggregator_Inventory</t>
+        </is>
+      </c>
+      <c r="C322" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:42:55</t>
+        </is>
+      </c>
+      <c r="B323" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_monthly_sales_summary</t>
+        </is>
+      </c>
+      <c r="C323" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:42:55</t>
+        </is>
+      </c>
+      <c r="B324" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_fact_sales</t>
+        </is>
+      </c>
+      <c r="C324" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:42:55</t>
+        </is>
+      </c>
+      <c r="B325" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_fact_inventory</t>
+        </is>
+      </c>
+      <c r="C325" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:42:55</t>
+        </is>
+      </c>
+      <c r="B326" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_inventory_level_by_stores</t>
+        </is>
+      </c>
+      <c r="C326" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:42:55</t>
+        </is>
+      </c>
+      <c r="B327" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_monthly_sales_summary</t>
+        </is>
+      </c>
+      <c r="C327" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:42:55</t>
+        </is>
+      </c>
+      <c r="B328" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_fact_sales</t>
+        </is>
+      </c>
+      <c r="C328" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:42:55</t>
+        </is>
+      </c>
+      <c r="B329" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_fact_inventory</t>
+        </is>
+      </c>
+      <c r="C329" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:42:55</t>
+        </is>
+      </c>
+      <c r="B330" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_inventory_level_by_stores</t>
+        </is>
+      </c>
+      <c r="C330" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:24</t>
+        </is>
+      </c>
+      <c r="B331" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_data_for_sales_file_to_stage</t>
+        </is>
+      </c>
+      <c r="C331" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:24</t>
+        </is>
+      </c>
+      <c r="B332" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_stores_data_from_oracle_to_stag</t>
+        </is>
+      </c>
+      <c r="C332" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:24</t>
+        </is>
+      </c>
+      <c r="B333" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_product_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C333" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:24</t>
+        </is>
+      </c>
+      <c r="B334" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_inventory_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C334" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:25</t>
+        </is>
+      </c>
+      <c r="B335" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_supplier_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C335" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:25</t>
+        </is>
+      </c>
+      <c r="B336" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loading_for_monthly_sales_summary</t>
+        </is>
+      </c>
+      <c r="C336" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:25</t>
+        </is>
+      </c>
+      <c r="B337" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loadin_for_fact_sales</t>
+        </is>
+      </c>
+      <c r="C337" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:25</t>
+        </is>
+      </c>
+      <c r="B338" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loading_for_fact_inventory</t>
+        </is>
+      </c>
+      <c r="C338" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:25</t>
+        </is>
+      </c>
+      <c r="B339" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loading_for_inventory_levl_by_stores</t>
+        </is>
+      </c>
+      <c r="C339" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:25</t>
+        </is>
+      </c>
+      <c r="B340" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_sales_file</t>
+        </is>
+      </c>
+      <c r="C340" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:25</t>
+        </is>
+      </c>
+      <c r="B341" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_product_file</t>
+        </is>
+      </c>
+      <c r="C341" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:25</t>
+        </is>
+      </c>
+      <c r="B342" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_inventory_file</t>
+        </is>
+      </c>
+      <c r="C342" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:26</t>
+        </is>
+      </c>
+      <c r="B343" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_supplier_file</t>
+        </is>
+      </c>
+      <c r="C343" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:26</t>
+        </is>
+      </c>
+      <c r="B344" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_sales_file</t>
+        </is>
+      </c>
+      <c r="C344" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:26</t>
+        </is>
+      </c>
+      <c r="B345" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_product_file</t>
+        </is>
+      </c>
+      <c r="C345" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:26</t>
+        </is>
+      </c>
+      <c r="B346" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_inventory_file</t>
+        </is>
+      </c>
+      <c r="C346" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:26</t>
+        </is>
+      </c>
+      <c r="B347" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_supplier_file</t>
+        </is>
+      </c>
+      <c r="C347" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:26</t>
+        </is>
+      </c>
+      <c r="B348" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Filter_Sales</t>
+        </is>
+      </c>
+      <c r="C348" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:26</t>
+        </is>
+      </c>
+      <c r="B349" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Router_High_Sales</t>
+        </is>
+      </c>
+      <c r="C349" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:26</t>
+        </is>
+      </c>
+      <c r="B350" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Router_Low_Sales</t>
+        </is>
+      </c>
+      <c r="C350" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:26</t>
+        </is>
+      </c>
+      <c r="B351" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Aggregator_Sales</t>
+        </is>
+      </c>
+      <c r="C351" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:26</t>
+        </is>
+      </c>
+      <c r="B352" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_joiner_sales_product_stores</t>
+        </is>
+      </c>
+      <c r="C352" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:27</t>
+        </is>
+      </c>
+      <c r="B353" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Aggregator_Inventory</t>
+        </is>
+      </c>
+      <c r="C353" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:27</t>
+        </is>
+      </c>
+      <c r="B354" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_monthly_sales_summary</t>
+        </is>
+      </c>
+      <c r="C354" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:27</t>
+        </is>
+      </c>
+      <c r="B355" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_fact_sales</t>
+        </is>
+      </c>
+      <c r="C355" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:27</t>
+        </is>
+      </c>
+      <c r="B356" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_fact_inventory</t>
+        </is>
+      </c>
+      <c r="C356" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:27</t>
+        </is>
+      </c>
+      <c r="B357" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_inventory_level_by_stores</t>
+        </is>
+      </c>
+      <c r="C357" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:27</t>
+        </is>
+      </c>
+      <c r="B358" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_monthly_sales_summary</t>
+        </is>
+      </c>
+      <c r="C358" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:27</t>
+        </is>
+      </c>
+      <c r="B359" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_fact_sales</t>
+        </is>
+      </c>
+      <c r="C359" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:27</t>
+        </is>
+      </c>
+      <c r="B360" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_fact_inventory</t>
+        </is>
+      </c>
+      <c r="C360" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:27</t>
+        </is>
+      </c>
+      <c r="B361" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_inventory_level_by_stores</t>
+        </is>
+      </c>
+      <c r="C361" s="1" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/etl_test_results.xlsx
+++ b/etl_test_results.xlsx
@@ -915,7 +915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C361"/>
+  <dimension ref="A1:C392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -7055,6 +7055,533 @@
         </is>
       </c>
     </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:52:25</t>
+        </is>
+      </c>
+      <c r="B362" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_data_for_sales_file_to_stage</t>
+        </is>
+      </c>
+      <c r="C362" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:52:25</t>
+        </is>
+      </c>
+      <c r="B363" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_stores_data_from_oracle_to_stag</t>
+        </is>
+      </c>
+      <c r="C363" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:52:25</t>
+        </is>
+      </c>
+      <c r="B364" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_product_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C364" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:52:25</t>
+        </is>
+      </c>
+      <c r="B365" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_inventory_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C365" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:52:25</t>
+        </is>
+      </c>
+      <c r="B366" s="1" t="inlineStr">
+        <is>
+          <t>test_extract_supplier_data_from_file_to_stag</t>
+        </is>
+      </c>
+      <c r="C366" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:52:25</t>
+        </is>
+      </c>
+      <c r="B367" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loading_for_monthly_sales_summary</t>
+        </is>
+      </c>
+      <c r="C367" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:52:25</t>
+        </is>
+      </c>
+      <c r="B368" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loadin_for_fact_sales</t>
+        </is>
+      </c>
+      <c r="C368" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:52:26</t>
+        </is>
+      </c>
+      <c r="B369" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loading_for_fact_inventory</t>
+        </is>
+      </c>
+      <c r="C369" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:52:26</t>
+        </is>
+      </c>
+      <c r="B370" s="1" t="inlineStr">
+        <is>
+          <t>test_data_loading_for_inventory_levl_by_stores</t>
+        </is>
+      </c>
+      <c r="C370" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:52:26</t>
+        </is>
+      </c>
+      <c r="B371" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_sales_file</t>
+        </is>
+      </c>
+      <c r="C371" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:52:26</t>
+        </is>
+      </c>
+      <c r="B372" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_product_file</t>
+        </is>
+      </c>
+      <c r="C372" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:52:26</t>
+        </is>
+      </c>
+      <c r="B373" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_inventory_file</t>
+        </is>
+      </c>
+      <c r="C373" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:52:26</t>
+        </is>
+      </c>
+      <c r="B374" s="1" t="inlineStr">
+        <is>
+          <t>test_duplicates_for_supplier_file</t>
+        </is>
+      </c>
+      <c r="C374" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:52:26</t>
+        </is>
+      </c>
+      <c r="B375" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_sales_file</t>
+        </is>
+      </c>
+      <c r="C375" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:52:26</t>
+        </is>
+      </c>
+      <c r="B376" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_product_file</t>
+        </is>
+      </c>
+      <c r="C376" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:52:26</t>
+        </is>
+      </c>
+      <c r="B377" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_inventory_file</t>
+        </is>
+      </c>
+      <c r="C377" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:52:27</t>
+        </is>
+      </c>
+      <c r="B378" s="1" t="inlineStr">
+        <is>
+          <t>test_null_for_supplier_file</t>
+        </is>
+      </c>
+      <c r="C378" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:52:27</t>
+        </is>
+      </c>
+      <c r="B379" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Filter_Sales</t>
+        </is>
+      </c>
+      <c r="C379" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:52:27</t>
+        </is>
+      </c>
+      <c r="B380" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Router_High_Sales</t>
+        </is>
+      </c>
+      <c r="C380" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:52:27</t>
+        </is>
+      </c>
+      <c r="B381" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Router_Low_Sales</t>
+        </is>
+      </c>
+      <c r="C381" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:52:27</t>
+        </is>
+      </c>
+      <c r="B382" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Aggregator_Sales</t>
+        </is>
+      </c>
+      <c r="C382" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:52:27</t>
+        </is>
+      </c>
+      <c r="B383" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_joiner_sales_product_stores</t>
+        </is>
+      </c>
+      <c r="C383" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:52:27</t>
+        </is>
+      </c>
+      <c r="B384" s="1" t="inlineStr">
+        <is>
+          <t>test_transform_Aggregator_Inventory</t>
+        </is>
+      </c>
+      <c r="C384" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:52:27</t>
+        </is>
+      </c>
+      <c r="B385" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_monthly_sales_summary</t>
+        </is>
+      </c>
+      <c r="C385" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:52:27</t>
+        </is>
+      </c>
+      <c r="B386" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_fact_sales</t>
+        </is>
+      </c>
+      <c r="C386" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:52:28</t>
+        </is>
+      </c>
+      <c r="B387" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_fact_inventory</t>
+        </is>
+      </c>
+      <c r="C387" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:52:28</t>
+        </is>
+      </c>
+      <c r="B388" s="1" t="inlineStr">
+        <is>
+          <t>test_columns_for_inventory_level_by_stores</t>
+        </is>
+      </c>
+      <c r="C388" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:52:28</t>
+        </is>
+      </c>
+      <c r="B389" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_monthly_sales_summary</t>
+        </is>
+      </c>
+      <c r="C389" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:52:28</t>
+        </is>
+      </c>
+      <c r="B390" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_fact_sales</t>
+        </is>
+      </c>
+      <c r="C390" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:52:28</t>
+        </is>
+      </c>
+      <c r="B391" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_fact_inventory</t>
+        </is>
+      </c>
+      <c r="C391" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:52:28</t>
+        </is>
+      </c>
+      <c r="B392" s="1" t="inlineStr">
+        <is>
+          <t>test_dtypes_for_inventory_level_by_stores</t>
+        </is>
+      </c>
+      <c r="C392" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
